--- a/artfynd/A 15862-2020 artfynd.xlsx
+++ b/artfynd/A 15862-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121136558</v>
       </c>
       <c r="B2" t="n">
-        <v>91086</v>
+        <v>91096</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 15862-2020 artfynd.xlsx
+++ b/artfynd/A 15862-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121136558</v>
       </c>
       <c r="B2" t="n">
-        <v>91096</v>
+        <v>91108</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 15862-2020 artfynd.xlsx
+++ b/artfynd/A 15862-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121136558</v>
       </c>
       <c r="B2" t="n">
-        <v>91108</v>
+        <v>91109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 15862-2020 artfynd.xlsx
+++ b/artfynd/A 15862-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121136558</v>
       </c>
       <c r="B2" t="n">
-        <v>91109</v>
+        <v>91112</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
